--- a/data/submissions.xlsx
+++ b/data/submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -647,9 +647,61 @@
         <v>/uploads/7037961955.jpg</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>6558861484</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Meherab Samir</v>
+      </c>
+      <c r="C11" t="str">
+        <v>RIIT</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-05-06T17:29:06.715Z</v>
+      </c>
+      <c r="F11" t="str">
+        <v>CST</v>
+      </c>
+      <c r="G11" t="str">
+        <v>01703856688</v>
+      </c>
+      <c r="H11" t="str">
+        <v>meherabsamir.me@gmail.com</v>
+      </c>
+      <c r="I11" t="str">
+        <v>/uploads/6558861484.jpg</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2031301630</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Morsalin Ikbal</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Rangpur Polytechnic Institute</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2026-05-06T17:55:33.498Z</v>
+      </c>
+      <c r="F12" t="str">
+        <v>MT</v>
+      </c>
+      <c r="G12" t="str">
+        <v>01581782193</v>
+      </c>
+      <c r="H12" t="str">
+        <v>mdnasirislam208@gmail.com</v>
+      </c>
+      <c r="I12" t="str">
+        <v>/uploads/2031301630.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/submissions.xlsx
+++ b/data/submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -699,9 +699,87 @@
         <v>/uploads/2031301630.jpg</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>6499423395</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Sipon Islam</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Rangpur Ideal Institute Of Technology</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2026-05-06T18:00:07.653Z</v>
+      </c>
+      <c r="F13" t="str">
+        <v>CT</v>
+      </c>
+      <c r="G13" t="str">
+        <v>01703856688</v>
+      </c>
+      <c r="H13" t="str">
+        <v>mahfuza9046@gmail.com</v>
+      </c>
+      <c r="I13" t="str">
+        <v>/uploads/6499423395.jpg</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2720516592</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Reyad  Mahmud</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Rangpur Polytechnic Institute</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2026-05-06T18:02:41.364Z</v>
+      </c>
+      <c r="F14" t="str">
+        <v>CT</v>
+      </c>
+      <c r="G14" t="str">
+        <v>01581782193</v>
+      </c>
+      <c r="H14" t="str">
+        <v>innowavesolutioninfo@gmail.com</v>
+      </c>
+      <c r="I14" t="str">
+        <v>/uploads/2720516592.jpg</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2165776608</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Ashikur Rahman Ovi</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Rangpur Polytechnic Instutute</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2026-05-06T20:34:52.881Z</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Computer Science And Technology</v>
+      </c>
+      <c r="G15" t="str">
+        <v>01581782193</v>
+      </c>
+      <c r="H15" t="str">
+        <v>ashikurovi2003@gmail.com</v>
+      </c>
+      <c r="I15" t="str">
+        <v>/uploads/2165776608.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
   </ignoredErrors>
 </worksheet>
 </file>